--- a/data/trans_camb/P36BPD07_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P36BPD07_R-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-18,19</t>
+          <t>-17,06</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-15,95</t>
+          <t>-16,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-16,78</t>
+          <t>-16,86</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,28; -13,72</t>
+          <t>-21,15; -13,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -13,14</t>
+          <t>-19,53; -13,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -14,39</t>
+          <t>-19,27; -14,54</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-19,91%</t>
+          <t>-18,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-16,95%</t>
+          <t>-17,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-18,06%</t>
+          <t>-18,14%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,06; -15,33</t>
+          <t>-23,02; -14,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,71; -14,08</t>
+          <t>-20,83; -15,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -15,54</t>
+          <t>-20,52; -15,74</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-8,78</t>
+          <t>-13,4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-9,12</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,87</t>
+          <t>-11,29</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; -0,24</t>
+          <t>-16,21; -10,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 1,77</t>
+          <t>-11,59; -6,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -1,62</t>
+          <t>-13,18; -9,04</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-10,84%</t>
+          <t>-16,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,97%</t>
+          <t>-11,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,4%</t>
+          <t>-13,81%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -0,19</t>
+          <t>-20,01; -13,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 2,17</t>
+          <t>-13,83; -8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -1,84</t>
+          <t>-16,04; -11,18</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-6,55</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,99</t>
+          <t>-5,79</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,66; -2,94</t>
+          <t>-10,58; -2,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -0,55</t>
+          <t>-9,21; -1,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -3,16</t>
+          <t>-8,64; -3,09</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-8,6%</t>
+          <t>-7,47%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-5,04%</t>
+          <t>-5,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,79%</t>
+          <t>-6,56%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -3,46</t>
+          <t>-11,87; -2,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -0,61</t>
+          <t>-10,28; -1,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -3,67</t>
+          <t>-9,63; -3,56</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-10,54</t>
+          <t>-12,95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,83</t>
+          <t>-10,47</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,14</t>
+          <t>-11,66</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -4,31</t>
+          <t>-15,15; -11,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -4,48</t>
+          <t>-12,2; -8,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -5,81</t>
+          <t>-12,99; -10,24</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-12,49%</t>
+          <t>-15,34%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-9,03%</t>
+          <t>-12,07%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,68%</t>
+          <t>-13,63%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -5,12</t>
+          <t>-17,82; -13,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,56; -5,16</t>
+          <t>-13,91; -10,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -6,78</t>
+          <t>-15,08; -12,02</t>
         </is>
       </c>
     </row>
